--- a/outputs/comparisons/td/2026_t1_vs_2025_t3/comparison.xlsx
+++ b/outputs/comparisons/td/2026_t1_vs_2025_t3/comparison.xlsx
@@ -2005,7 +2005,7 @@
       <c r="H30" s="4" t="inlineStr"/>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>Le changement est pertinent car il implique la suppression d'un tableau entier lié à la gestion du capital. Cela peut affecter la transparence et la compréhension des expositions nettes par région et contrepartie, ce qui est crucial pour l'évaluation des risques géographiques. Il s'agit d'une suppression structurelle qui pourrait nécessiter une révision des pratiques de divulgation.</t>
+          <t>(1) Le changement est pertinent car il implique la suppression d'un tableau entier lié à la gestion du capital ; (2) Cela peut affecter la transparence et la compréhension des expositions nettes par région et contrepartie, ce qui est crucial pour l'évaluation des risques géographiques ; (3) Il s'agit d'une suppression structurelle qui pourrait indiquer un changement dans la manière dont la banque gère ou divulgue ses expositions.</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
